--- a/artfynd/A 11544-2024 artfynd.xlsx
+++ b/artfynd/A 11544-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112329598</v>
+        <v>205994</v>
       </c>
       <c r="B2" t="n">
-        <v>89612</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ögonfägnaden, Jmt</t>
+          <t>Öster Sännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546458</v>
+        <v>546524</v>
       </c>
       <c r="R2" t="n">
-        <v>7039992</v>
+        <v>7040080</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2012-06-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2012-06-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Åsa Stenman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112329597</v>
+        <v>1979682</v>
       </c>
       <c r="B3" t="n">
-        <v>77442</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +787,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ögonfägnaden, Jmt</t>
+          <t>Öster Sännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546538</v>
+        <v>546471</v>
       </c>
       <c r="R3" t="n">
-        <v>7039958</v>
+        <v>7040142</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2012-06-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2012-06-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,65 +861,64 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Åsa Stenman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112329596</v>
+        <v>4396196</v>
       </c>
       <c r="B4" t="n">
-        <v>77442</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ögonfägnaden, Jmt</t>
+          <t>Öster Sännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546369</v>
+        <v>546506</v>
       </c>
       <c r="R4" t="n">
-        <v>7040163</v>
+        <v>7040115</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2012-06-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2012-06-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,15 +962,314 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Åsa Stenman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>112329596</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ögonfägnaden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>546369</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7040163</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Maria Edstam</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Maria Edstam</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>112329597</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ögonfägnaden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>546537</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7039958</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6633304</v>
+      </c>
+      <c r="B7" t="n">
+        <v>95765</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1004672</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Källmossor</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Philonotis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Brid.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Öster Sännsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>546463</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7040164</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2012-06-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2012-06-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Åsa Stenman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11544-2024 artfynd.xlsx
+++ b/artfynd/A 11544-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/205994</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1979682</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4396196</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112329596</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112329597</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1270,8 +1300,21 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6633304</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>